--- a/data/trans_dic/IP25A_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Estudios-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 41,28</t>
+          <t>12,55; 31,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 31,45</t>
+          <t>9,57; 29,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 30,62</t>
+          <t>13,31; 27,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,04; 16,6</t>
+          <t>10,25; 15,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,99</t>
+          <t>10,73; 16,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 15,14</t>
+          <t>11,3; 15,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 19,5</t>
+          <t>9,03; 19,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,84</t>
+          <t>9,98; 19,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,02; 16,99</t>
+          <t>10,27; 17,25</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 16,51</t>
+          <t>11,64; 16,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,22</t>
+          <t>11,51; 15,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,72</t>
+          <t>12,14; 15,43</t>
         </is>
       </c>
     </row>
@@ -774,18 +774,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>19520</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5296; 21059</t>
+          <t>7062; 17657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7898; 19317</t>
+          <t>4149; 12912</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16255; 34428</t>
+          <t>13261; 27432</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>67481</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126831</t>
+          <t>117489</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45510; 75256</t>
+          <t>48502; 74538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53567; 82199</t>
+          <t>45633; 69552</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107707; 146441</t>
+          <t>101534; 138724</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23509</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>42937</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14090; 28951</t>
+          <t>15208; 33149</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15222; 32709</t>
+          <t>14871; 29187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33258; 56380</t>
+          <t>32613; 54765</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>89729</t>
+          <t>96010</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72595; 107776</t>
+          <t>81248; 112983</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87401; 123075</t>
+          <t>71092; 98544</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170618; 221940</t>
+          <t>159662; 202970</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,55; 31,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 29,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13,31; 27,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,25; 15,75</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,73; 16,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,3; 15,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 19,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,98; 19,58</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10,27; 17,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11,64; 16,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11,51; 15,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12,14; 15,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2056601853868272</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.183417089952143</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1959804450027878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11570</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7950</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1255289631446774</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.09571622693288653</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1331350166552515</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7062; 17657</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4149; 12912</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13261; 27432</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3138575540135861</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2978787448914863</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2754086968792407</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1310497087925224</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1304664181466644</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1307736566307267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>62016</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>55473</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>117489</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1024918674213298</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1073231321161849</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1130148110027589</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>48502; 74538</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>45633; 69552</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>101534; 138724</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1575106142777553</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1635795449745585</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1544102282481675</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1331425561845882</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1376384155046406</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1352532390722469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>22424</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20513</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42937</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.09030019693543699</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.09978197958662889</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.102733715880365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>15208; 33149</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14871; 29187</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>32613; 54765</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1968241899321165</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1958393724212573</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1725141747559646</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1375691519454732</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1359136615027451</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1367919531570495</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>96010</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>83936</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>179946</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1164182585190881</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.115115548088638</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1213721238370593</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>81248; 112983</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>71092; 98544</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159662; 202970</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1618900306941603</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1595660926028799</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1542941432089394</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>11570</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>7950</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>19520</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>7062</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4149</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13261</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>17657</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>12912</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>27432</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>62016</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>55473</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>117489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>48502</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>45633</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>101534</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>74538</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>69552</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>138724</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>22424</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>20513</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>42937</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>15208</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>14871</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>32613</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>33149</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>29187</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>54765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>96010</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>83936</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>179946</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>81248</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>71092</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>159662</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>112983</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>98544</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>202970</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>